--- a/master/result/41_创业女王_从失业到商业帝国/41_创业女王_从失业到商业帝国.xlsx
+++ b/master/result/41_创业女王_从失业到商业帝国/41_创业女王_从失业到商业帝国.xlsx
@@ -397,566 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>day</v>
       </c>
       <c r="B2" t="str">
-        <v>day</v>
+        <v>/day/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>天</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>unemployment</v>
       </c>
       <c r="B3" t="str">
-        <v>unemployment</v>
+        <v>/unemployment/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>失业</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>outset</v>
       </c>
       <c r="B4" t="str">
-        <v>outset</v>
+        <v>/outset/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>开始</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>adverse</v>
       </c>
       <c r="B5" t="str">
-        <v>adverse</v>
+        <v>/adverse/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>不利的</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>TV</v>
       </c>
       <c r="B6" t="str">
-        <v>TV</v>
+        <v>/TV/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>电视</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>smart</v>
       </c>
       <c r="B7" t="str">
-        <v>smart</v>
+        <v>/smart/</v>
       </c>
       <c r="C7" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>聪明的</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>problem</v>
       </c>
       <c r="B8" t="str">
-        <v>problem</v>
+        <v>/problem/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>问题</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>expensive</v>
       </c>
       <c r="B9" t="str">
-        <v>expensive</v>
+        <v>/expensive/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>昂贵的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>propose</v>
       </c>
       <c r="B10" t="str">
-        <v>propose</v>
+        <v>/propose/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>提议</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>crew</v>
       </c>
       <c r="B11" t="str">
-        <v>crew</v>
+        <v>/kruː/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>全体船员</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>lab</v>
       </c>
       <c r="B12" t="str">
-        <v>lab</v>
+        <v>/lab/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>实验室</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>analyse</v>
       </c>
       <c r="B13" t="str">
-        <v>analyse</v>
+        <v>/ˈænəlaɪz/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>分析</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>overcoat</v>
       </c>
       <c r="B14" t="str">
-        <v>overcoat</v>
+        <v>/overcoat/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>大衣</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>postman</v>
       </c>
       <c r="B15" t="str">
-        <v>postman</v>
+        <v>/postman/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>邮递员</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>courtesy</v>
       </c>
       <c r="B16" t="str">
-        <v>courtesy</v>
+        <v>/courtesy/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>谦恭有礼</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>revenue</v>
       </c>
       <c r="B17" t="str">
-        <v>revenue</v>
+        <v>/revenue/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>财政收入</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>siren</v>
       </c>
       <c r="B18" t="str">
-        <v>siren</v>
+        <v>/siren/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>警报声</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>fake</v>
       </c>
       <c r="B19" t="str">
-        <v>fake</v>
+        <v>/fake/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>假的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>scarcely</v>
       </c>
       <c r="B20" t="str">
-        <v>scarcely</v>
+        <v>/scarcely/</v>
       </c>
       <c r="C20" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D20" t="str">
         <v>几乎不</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>quiz</v>
       </c>
       <c r="B21" t="str">
-        <v>quiz</v>
+        <v>/quiz/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>小型考试</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>contain</v>
       </c>
       <c r="B22" t="str">
-        <v>contain</v>
+        <v>/kənˈteɪn/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>包含</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>mechanism</v>
       </c>
       <c r="B23" t="str">
-        <v>mechanism</v>
+        <v>/mechanism/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>机械装置</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>scale</v>
       </c>
       <c r="B24" t="str">
-        <v>scale</v>
+        <v>/scale/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>规模</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>typical</v>
       </c>
       <c r="B25" t="str">
-        <v>typical</v>
+        <v>/typical/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>典型的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>blunt</v>
       </c>
       <c r="B26" t="str">
-        <v>blunt</v>
+        <v>/blunt/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>率直的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>borrow</v>
       </c>
       <c r="B27" t="str">
-        <v>borrow</v>
+        <v>/ˈbɒrəʊ/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>借</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>own</v>
       </c>
       <c r="B28" t="str">
-        <v>own</v>
+        <v>/əʊn/</v>
       </c>
       <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>自己的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>panel</v>
       </c>
       <c r="B29" t="str">
-        <v>panel</v>
+        <v>/panel/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>控制板</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>cool</v>
       </c>
       <c r="B30" t="str">
-        <v>cool</v>
+        <v>/kuːl/</v>
       </c>
       <c r="C30" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D30" t="str">
         <v>冷静的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>republican</v>
       </c>
       <c r="B31" t="str">
-        <v>republican</v>
+        <v>/republican/</v>
       </c>
       <c r="C31" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D31" t="str">
         <v>共和的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>bibliography</v>
       </c>
       <c r="B32" t="str">
-        <v>bibliography</v>
+        <v>/bibliography/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>参考书目</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>toast</v>
       </c>
       <c r="B33" t="str">
-        <v>toast</v>
+        <v>/toast/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>烤面包</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>colony</v>
       </c>
       <c r="B34" t="str">
-        <v>colony</v>
+        <v>/ˈkɒləni/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>殖民地</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>retreat</v>
       </c>
       <c r="B35" t="str">
-        <v>retreat</v>
+        <v>/retreat/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>撤退</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>comic</v>
       </c>
       <c r="B36" t="str">
-        <v>comic</v>
+        <v>/comic/</v>
       </c>
       <c r="C36" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>喜剧的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>interference</v>
       </c>
       <c r="B37" t="str">
-        <v>interference</v>
+        <v>/interference/</v>
       </c>
       <c r="C37" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>干扰</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>appearance</v>
       </c>
       <c r="B38" t="str">
-        <v>appearance</v>
+        <v>/appearance/</v>
       </c>
       <c r="C38" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>外表</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>channel</v>
       </c>
       <c r="B39" t="str">
-        <v>channel</v>
+        <v>/ˈtʃænəl/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>渠道</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>price</v>
       </c>
       <c r="B40" t="str">
-        <v>price</v>
+        <v>/price/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>价格</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>provided</v>
       </c>
       <c r="B41" t="str">
-        <v>provided</v>
+        <v>/provided/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>倘若</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>prince</v>
       </c>
       <c r="B42" t="str">
-        <v>prince</v>
+        <v>/prince/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>王子</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>servant</v>
       </c>
       <c r="B43" t="str">
-        <v>servant</v>
+        <v>/servant/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>仆人</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>occupation</v>
       </c>
       <c r="B44" t="str">
-        <v>occupation</v>
+        <v>/occupation/</v>
       </c>
       <c r="C44" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>职业</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>master</v>
       </c>
       <c r="B45" t="str">
-        <v>master</v>
+        <v>/master/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>男主人</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>protest</v>
       </c>
       <c r="B46" t="str">
-        <v>protest</v>
+        <v>/protest/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>抗议</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>image</v>
       </c>
       <c r="B47" t="str">
-        <v>image</v>
+        <v>/image/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>形象</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>lead</v>
       </c>
       <c r="B48" t="str">
-        <v>lead</v>
+        <v>/liːd/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>带领</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>revive</v>
       </c>
       <c r="B49" t="str">
-        <v>revive</v>
+        <v>/revive/</v>
       </c>
       <c r="C49" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>恢复</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>impair</v>
       </c>
       <c r="B50" t="str">
-        <v>impair</v>
+        <v>/impair/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>损害</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>